--- a/emdb/data/classifications/equivalence.xlsx
+++ b/emdb/data/classifications/equivalence.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="FAOSTAT COUNTRIES" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="1543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2495" uniqueCount="1542">
   <si>
     <t xml:space="preserve">Area Code</t>
   </si>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">Manufacturing Industries and Construction</t>
   </si>
   <si>
-    <t xml:space="preserve"> 9999</t>
+    <t xml:space="preserve">9999</t>
   </si>
   <si>
     <t xml:space="preserve">Undetermined</t>
@@ -4449,9 +4449,6 @@
   </si>
   <si>
     <t xml:space="preserve">Activities of extraterritorial organizations and bodies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9999</t>
   </si>
   <si>
     <t xml:space="preserve">Transaction</t>
@@ -8882,7 +8879,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B421"/>
+  <dimension ref="A1:B422"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="107.86"/>
@@ -9202,3057 +9199,3065 @@
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>745</v>
+        <v>611</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>746</v>
+        <v>612</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>615</v>
+        <v>747</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>616</v>
+        <v>748</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>749</v>
+        <v>615</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>750</v>
+        <v>616</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>581</v>
+        <v>859</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>582</v>
+        <v>860</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>631</v>
+        <v>581</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>632</v>
+        <v>582</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>665</v>
+        <v>631</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>666</v>
+        <v>632</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>861</v>
+        <v>665</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>862</v>
+        <v>666</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>625</v>
+        <v>879</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>626</v>
+        <v>880</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>881</v>
+        <v>625</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>882</v>
+        <v>626</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>619</v>
+        <v>885</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>620</v>
+        <v>886</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>887</v>
+        <v>619</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>888</v>
+        <v>620</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>635</v>
+        <v>891</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>636</v>
+        <v>892</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>893</v>
+        <v>635</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>894</v>
+        <v>636</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>641</v>
+        <v>919</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>642</v>
+        <v>920</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>921</v>
+        <v>641</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>922</v>
+        <v>642</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>577</v>
+        <v>1029</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>578</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>1031</v>
+        <v>577</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>1032</v>
+        <v>578</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>659</v>
+        <v>1033</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>660</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>1035</v>
+        <v>659</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>1036</v>
+        <v>660</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>649</v>
+        <v>1039</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>650</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>1041</v>
+        <v>653</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1042</v>
+        <v>654</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="1" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="1" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="s">
-        <v>603</v>
+        <v>1157</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>604</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>594</v>
+        <v>604</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="1" t="s">
-        <v>1159</v>
+        <v>593</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>1160</v>
+        <v>594</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="1" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="1" t="s">
-        <v>599</v>
+        <v>1161</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>600</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>1163</v>
+        <v>599</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>1164</v>
+        <v>600</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="s">
-        <v>589</v>
+        <v>1165</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>590</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="s">
-        <v>1167</v>
+        <v>589</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>1168</v>
+        <v>590</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="1" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="1" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="1" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="1" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="1" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="1" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="1" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="1" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="1" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="1" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="1" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="1" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="1" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="1" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="1" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="1" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="1" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="1" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="1" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="1" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="1" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="1" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="1" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="1" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="1" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="1" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="1" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="1" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="1" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="1" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="1" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="1" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="1" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="1" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="1" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="1" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="1" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="1" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="1" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="1" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="1" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="1" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="1" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="1" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="1" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="1" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="1" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="1" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="1" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="1" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="1" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="1" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="1" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="1" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="1" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="1" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="1" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="1" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="1" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="1" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="1" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="1" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="1" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="1" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="1" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A421" s="1" t="s">
         <v>1473</v>
       </c>
-      <c r="B420" s="1" t="s">
+      <c r="B421" s="1" t="s">
         <v>1474</v>
       </c>
     </row>
-    <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A421" s="3" t="s">
-        <v>1475</v>
-      </c>
-      <c r="B421" s="3" t="s">
+    <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A422" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="B422" s="3" t="s">
         <v>586</v>
       </c>
     </row>
@@ -12281,7 +12286,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>669</v>
@@ -12292,7 +12297,7 @@
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>671</v>
@@ -12303,7 +12308,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>667</v>
@@ -12314,7 +12319,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>673</v>
@@ -12325,7 +12330,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>675</v>
@@ -12336,7 +12341,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>677</v>
@@ -12347,7 +12352,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>679</v>
@@ -12358,7 +12363,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>681</v>
@@ -12369,7 +12374,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>683</v>
@@ -12380,7 +12385,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>685</v>
@@ -12391,7 +12396,7 @@
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>751</v>
@@ -12408,7 +12413,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>689</v>
@@ -12419,7 +12424,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>691</v>
@@ -12430,7 +12435,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>693</v>
@@ -12441,7 +12446,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>695</v>
@@ -12452,7 +12457,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>697</v>
@@ -12463,7 +12468,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>699</v>
@@ -12474,7 +12479,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>701</v>
@@ -12485,7 +12490,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>703</v>
@@ -12496,7 +12501,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>705</v>
@@ -12507,7 +12512,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>707</v>
@@ -12518,7 +12523,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>709</v>
@@ -12529,7 +12534,7 @@
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>711</v>
@@ -12540,7 +12545,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>713</v>
@@ -12551,7 +12556,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>715</v>
@@ -12562,7 +12567,7 @@
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>717</v>
@@ -12573,7 +12578,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>719</v>
@@ -12584,7 +12589,7 @@
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>721</v>
@@ -12595,7 +12600,7 @@
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>723</v>
@@ -12606,7 +12611,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>725</v>
@@ -12617,7 +12622,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>727</v>
@@ -12628,7 +12633,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>729</v>
@@ -12639,7 +12644,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>731</v>
@@ -12650,7 +12655,7 @@
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>733</v>
@@ -12661,7 +12666,7 @@
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>735</v>
@@ -12672,7 +12677,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>737</v>
@@ -12683,7 +12688,7 @@
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>739</v>
@@ -12694,7 +12699,7 @@
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>741</v>
@@ -12705,7 +12710,7 @@
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>743</v>
@@ -12716,7 +12721,7 @@
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>745</v>
@@ -12727,7 +12732,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>747</v>
@@ -12738,7 +12743,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>615</v>
@@ -12749,7 +12754,7 @@
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>749</v>
@@ -12760,7 +12765,7 @@
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>751</v>
@@ -12771,7 +12776,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>753</v>
@@ -12782,7 +12787,7 @@
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>755</v>
@@ -12793,7 +12798,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>757</v>
@@ -12804,7 +12809,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>759</v>
@@ -12815,7 +12820,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>761</v>
@@ -12826,7 +12831,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>763</v>
@@ -12837,7 +12842,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>765</v>
@@ -12848,7 +12853,7 @@
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>767</v>
@@ -12859,7 +12864,7 @@
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>769</v>
@@ -12870,7 +12875,7 @@
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>771</v>
@@ -12881,7 +12886,7 @@
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>773</v>
@@ -12892,7 +12897,7 @@
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>775</v>
@@ -12903,7 +12908,7 @@
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>777</v>
@@ -12914,7 +12919,7 @@
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>779</v>
@@ -12925,7 +12930,7 @@
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>781</v>
@@ -12936,7 +12941,7 @@
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>783</v>
@@ -12947,7 +12952,7 @@
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>785</v>
@@ -12958,7 +12963,7 @@
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>787</v>
@@ -12969,7 +12974,7 @@
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>789</v>
@@ -12980,7 +12985,7 @@
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>791</v>
@@ -12991,7 +12996,7 @@
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>793</v>
@@ -13002,7 +13007,7 @@
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>795</v>
@@ -13013,7 +13018,7 @@
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>797</v>
